--- a/AAII_Financials/Quarterly/VEOEY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VEOEY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="92">
   <si>
     <t>VEOEY</t>
   </si>
@@ -656,173 +656,181 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -865,83 +873,89 @@
       <c r="P8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S8" s="3">
         <v>11366200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>21974800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>10810300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>16113000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>7228000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>14436500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>7201800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>13880700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>6531500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>13540400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>7281800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>15654700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>7889100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>15674200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>8116200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>15807600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>6867200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>13942400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>7068900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>14172900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>6513000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>13673100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>7267100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>14498800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AQ8" s="3">
         <v>6730500</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -987,80 +1001,86 @@
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R9" s="3">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T9" s="3">
         <v>18242800</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V9" s="3">
         <v>13423800</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X9" s="3">
         <v>11883000</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z9" s="3">
         <v>11479900</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB9" s="3">
         <v>11580300</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD9" s="3">
         <v>13043100</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF9" s="3">
         <v>12935200</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH9" s="3">
         <v>13105100</v>
       </c>
-      <c r="AG9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ9" s="3">
         <v>11413600</v>
       </c>
-      <c r="AI9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL9" s="3">
         <v>11652900</v>
       </c>
-      <c r="AK9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN9" s="3">
         <v>11155500</v>
       </c>
-      <c r="AM9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP9" s="3">
         <v>12109800</v>
       </c>
-      <c r="AO9" s="3" t="s">
+      <c r="AQ9" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1106,80 +1126,86 @@
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R10" s="3">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T10" s="3">
         <v>3732100</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V10" s="3">
         <v>2689200</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X10" s="3">
         <v>2553500</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z10" s="3">
         <v>2400800</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB10" s="3">
         <v>1960000</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD10" s="3">
         <v>2611600</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF10" s="3">
         <v>2739000</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH10" s="3">
         <v>2702500</v>
       </c>
-      <c r="AG10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ10" s="3">
         <v>2528800</v>
       </c>
-      <c r="AI10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL10" s="3">
         <v>2520000</v>
       </c>
-      <c r="AK10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN10" s="3">
         <v>2517600</v>
       </c>
-      <c r="AM10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP10" s="3">
         <v>2388900</v>
       </c>
-      <c r="AO10" s="3" t="s">
+      <c r="AQ10" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1221,8 +1247,10 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1340,8 +1368,14 @@
       <c r="AO12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1459,8 +1493,14 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1506,80 +1546,86 @@
       <c r="Q14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3">
         <v>181600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>79400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>185500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>83200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>188500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>69000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>291200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>127100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>137300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>66400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>279300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>85900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>188000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AG14" s="3">
         <v>81300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>263200</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AI14" s="3">
         <v>68900</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AJ14" s="3">
         <v>195900</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AK14" s="3">
         <v>75200</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AL14" s="3">
         <v>236500</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AM14" s="3">
         <v>80700</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AN14" s="3">
         <v>247600</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AO14" s="3">
         <v>76400</v>
       </c>
-      <c r="AN14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ14" s="3">
         <v>77900</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1628,77 +1674,83 @@
       <c r="R15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S15" s="3">
+      <c r="S15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U15" s="3">
         <v>798700</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W15" s="3">
         <v>878900</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y15" s="3">
         <v>558400</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA15" s="3">
         <v>690700</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC15" s="3">
         <v>584100</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE15" s="3">
         <v>641500</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG15" s="3">
         <v>617000</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI15" s="3">
         <v>565900</v>
       </c>
-      <c r="AH15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK15" s="3">
         <v>548700</v>
       </c>
-      <c r="AJ15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM15" s="3">
         <v>1376200</v>
       </c>
-      <c r="AL15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO15" s="3">
         <v>473000</v>
       </c>
-      <c r="AN15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ15" s="3">
         <v>472000</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1737,8 +1789,10 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1784,80 +1838,86 @@
       <c r="Q17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R17" s="3">
+      <c r="R17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T17" s="3">
         <v>20750800</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V17" s="3">
         <v>15547800</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X17" s="3">
         <v>13705000</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z17" s="3">
         <v>13312500</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB17" s="3">
         <v>13265100</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD17" s="3">
         <v>14983000</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF17" s="3">
         <v>14803600</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH17" s="3">
         <v>15036900</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ17" s="3">
         <v>13175700</v>
       </c>
-      <c r="AI17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL17" s="3">
         <v>13524100</v>
       </c>
-      <c r="AK17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN17" s="3">
         <v>13015600</v>
       </c>
-      <c r="AM17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP17" s="3">
         <v>13922000</v>
       </c>
-      <c r="AO17" s="3" t="s">
+      <c r="AQ17" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1903,80 +1963,86 @@
       <c r="Q18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T18" s="3">
         <v>1224000</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V18" s="3">
         <v>565100</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X18" s="3">
         <v>731500</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z18" s="3">
         <v>568300</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB18" s="3">
         <v>275200</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD18" s="3">
         <v>671700</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF18" s="3">
         <v>870700</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH18" s="3">
         <v>770700</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>766700</v>
       </c>
-      <c r="AI18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL18" s="3">
         <v>648700</v>
       </c>
-      <c r="AK18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN18" s="3">
         <v>657500</v>
       </c>
-      <c r="AM18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP18" s="3">
         <v>576800</v>
       </c>
-      <c r="AO18" s="3" t="s">
+      <c r="AQ18" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2018,8 +2084,10 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2065,80 +2133,86 @@
       <c r="Q20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T20" s="3">
         <v>-223000</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V20" s="3">
         <v>-83400</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X20" s="3">
         <v>87100</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-11400</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-75100</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD20" s="3">
         <v>258300</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-4200</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-94900</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-50900</v>
       </c>
-      <c r="AI20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL20" s="3">
         <v>-48800</v>
       </c>
-      <c r="AK20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN20" s="3">
         <v>-59900</v>
       </c>
-      <c r="AM20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP20" s="3">
         <v>-54800</v>
       </c>
-      <c r="AO20" s="3" t="s">
+      <c r="AQ20" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2190,74 +2264,80 @@
       <c r="S21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V21" s="3">
         <v>2777000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z21" s="3">
         <v>2657900</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="3">
         <v>3220000</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF21" s="3">
         <v>1976100</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH21" s="3">
         <v>1771200</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>1695400</v>
       </c>
-      <c r="AI21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL21" s="3">
         <v>1426000</v>
       </c>
-      <c r="AK21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN21" s="3">
         <v>1433700</v>
       </c>
-      <c r="AM21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP21" s="3">
         <v>1491400</v>
       </c>
-      <c r="AO21" s="3" t="s">
+      <c r="AQ21" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2303,80 +2383,86 @@
       <c r="Q22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R22" s="3">
+      <c r="R22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T22" s="3">
         <v>312300</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V22" s="3">
         <v>175900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>46300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>164100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>7800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>176600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>7000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>207900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>9900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>211100</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF22" s="3">
         <v>237900</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH22" s="3">
         <v>235900</v>
       </c>
-      <c r="AG22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>182500</v>
       </c>
-      <c r="AI22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL22" s="3">
         <v>199800</v>
       </c>
-      <c r="AK22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN22" s="3">
         <v>199700</v>
       </c>
-      <c r="AM22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP22" s="3">
         <v>210300</v>
       </c>
-      <c r="AO22" s="3" t="s">
+      <c r="AQ22" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2422,80 +2508,86 @@
       <c r="Q23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R23" s="3">
+      <c r="R23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T23" s="3">
         <v>688800</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V23" s="3">
         <v>305800</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X23" s="3">
         <v>654500</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z23" s="3">
         <v>380200</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB23" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD23" s="3">
         <v>718900</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF23" s="3">
         <v>628600</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH23" s="3">
         <v>439900</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ23" s="3">
         <v>533200</v>
       </c>
-      <c r="AI23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL23" s="3">
         <v>400100</v>
       </c>
-      <c r="AK23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN23" s="3">
         <v>397900</v>
       </c>
-      <c r="AM23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP23" s="3">
         <v>311600</v>
       </c>
-      <c r="AO23" s="3" t="s">
+      <c r="AQ23" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2541,80 +2633,86 @@
       <c r="Q24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R24" s="3">
+      <c r="R24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T24" s="3">
         <v>254400</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V24" s="3">
         <v>138500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>24800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>230600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>98200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>83500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>44100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>60200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>67500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>225400</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF24" s="3">
         <v>116300</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH24" s="3">
         <v>89100</v>
       </c>
-      <c r="AG24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>137000</v>
       </c>
-      <c r="AI24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL24" s="3">
         <v>124700</v>
       </c>
-      <c r="AK24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN24" s="3">
         <v>119000</v>
       </c>
-      <c r="AM24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP24" s="3">
         <v>77100</v>
       </c>
-      <c r="AO24" s="3" t="s">
+      <c r="AQ24" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2732,8 +2830,14 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2779,80 +2883,86 @@
       <c r="Q26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R26" s="3">
+      <c r="R26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T26" s="3">
         <v>434400</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V26" s="3">
         <v>167300</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X26" s="3">
         <v>423800</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z26" s="3">
         <v>296700</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB26" s="3">
         <v>-68000</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD26" s="3">
         <v>493500</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF26" s="3">
         <v>512200</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH26" s="3">
         <v>350800</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>396200</v>
       </c>
-      <c r="AI26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL26" s="3">
         <v>275400</v>
       </c>
-      <c r="AK26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN26" s="3">
         <v>278800</v>
       </c>
-      <c r="AM26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP26" s="3">
         <v>234500</v>
       </c>
-      <c r="AO26" s="3" t="s">
+      <c r="AQ26" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2898,80 +3008,86 @@
       <c r="Q27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R27" s="3">
+      <c r="R27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T27" s="3">
         <v>259000</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V27" s="3">
         <v>107500</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X27" s="3">
         <v>322800</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z27" s="3">
         <v>242200</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB27" s="3">
         <v>-140300</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD27" s="3">
         <v>439800</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF27" s="3">
         <v>408600</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH27" s="3">
         <v>177200</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>226300</v>
       </c>
-      <c r="AI27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL27" s="3">
         <v>219000</v>
       </c>
-      <c r="AK27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN27" s="3">
         <v>130400</v>
       </c>
-      <c r="AM27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP27" s="3">
         <v>287900</v>
       </c>
-      <c r="AO27" s="3" t="s">
+      <c r="AQ27" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3089,8 +3205,14 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3136,80 +3258,86 @@
       <c r="Q29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R29" s="3">
+      <c r="R29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T29" s="3">
         <v>-2200</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V29" s="3">
         <v>5000</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X29" s="3">
         <v>-4900</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-11100</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-9800</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-108400</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-18700</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-49400</v>
       </c>
-      <c r="AI29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3">
         <v>4400</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN29" s="3">
         <v>16400</v>
       </c>
-      <c r="AM29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP29" s="3">
         <v>-53300</v>
       </c>
-      <c r="AO29" s="3" t="s">
+      <c r="AQ29" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3327,8 +3455,14 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3446,8 +3580,14 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3493,80 +3633,86 @@
       <c r="Q32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T32" s="3">
         <v>223000</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V32" s="3">
         <v>83400</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X32" s="3">
         <v>-87100</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z32" s="3">
         <v>11400</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB32" s="3">
         <v>75100</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-258300</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF32" s="3">
         <v>4200</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH32" s="3">
         <v>94900</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>50900</v>
       </c>
-      <c r="AI32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL32" s="3">
         <v>48800</v>
       </c>
-      <c r="AK32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN32" s="3">
         <v>59900</v>
       </c>
-      <c r="AM32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP32" s="3">
         <v>54800</v>
       </c>
-      <c r="AO32" s="3" t="s">
+      <c r="AQ32" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3612,80 +3758,86 @@
       <c r="Q33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R33" s="3">
+      <c r="R33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T33" s="3">
         <v>256800</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V33" s="3">
         <v>112500</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X33" s="3">
         <v>317900</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z33" s="3">
         <v>231100</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB33" s="3">
         <v>-150100</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD33" s="3">
         <v>331400</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF33" s="3">
         <v>389900</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH33" s="3">
         <v>175100</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>176900</v>
       </c>
-      <c r="AI33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL33" s="3">
         <v>223400</v>
       </c>
-      <c r="AK33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN33" s="3">
         <v>146800</v>
       </c>
-      <c r="AM33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP33" s="3">
         <v>234600</v>
       </c>
-      <c r="AO33" s="3" t="s">
+      <c r="AQ33" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3803,8 +3955,14 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3850,204 +4008,216 @@
       <c r="Q35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R35" s="3">
+      <c r="R35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T35" s="3">
         <v>256800</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V35" s="3">
         <v>112500</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X35" s="3">
         <v>317900</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z35" s="3">
         <v>231100</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB35" s="3">
         <v>-150100</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD35" s="3">
         <v>331400</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF35" s="3">
         <v>389900</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH35" s="3">
         <v>175100</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>176900</v>
       </c>
-      <c r="AI35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL35" s="3">
         <v>223400</v>
       </c>
-      <c r="AK35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN35" s="3">
         <v>146800</v>
       </c>
-      <c r="AM35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP35" s="3">
         <v>234600</v>
       </c>
-      <c r="AO35" s="3" t="s">
+      <c r="AQ35" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4089,8 +4259,10 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4132,56 +4304,58 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8326300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>8403100</v>
+      </c>
+      <c r="F41" s="3">
         <v>9417600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>9411000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>8608300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>7922600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>9940000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>10708200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>8064900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>8120600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>9612000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>9204100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>8624000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>8582800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>9631300</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>5</v>
       </c>
@@ -4209,98 +4383,104 @@
       <c r="AA41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AB41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD41" s="3">
         <v>6597700</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF41" s="3">
         <v>4512100</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH41" s="3">
         <v>5389900</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ41" s="3">
         <v>3244600</v>
       </c>
-      <c r="AI41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL41" s="3">
         <v>7028000</v>
       </c>
-      <c r="AK41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN41" s="3">
         <v>5414300</v>
       </c>
-      <c r="AM41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP41" s="3">
         <v>6481100</v>
       </c>
-      <c r="AO41" s="3" t="s">
+      <c r="AQ41" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2537400</v>
+      </c>
+      <c r="E42" s="3">
+        <v>2560800</v>
+      </c>
+      <c r="F42" s="3">
         <v>2493800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>2492100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>2502600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>2303300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>2288000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>2464900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>2283300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>2299100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>2310200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>2212100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>2403600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>2392100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>1979300</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>5</v>
       </c>
@@ -4328,98 +4508,104 @@
       <c r="AA42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AB42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD42" s="3">
         <v>930900</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF42" s="3">
         <v>991700</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH42" s="3">
         <v>628700</v>
       </c>
-      <c r="AG42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ42" s="3">
         <v>803700</v>
       </c>
-      <c r="AI42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL42" s="3">
         <v>675300</v>
       </c>
-      <c r="AK42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN42" s="3">
         <v>791700</v>
       </c>
-      <c r="AM42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP42" s="3">
         <v>500400</v>
       </c>
-      <c r="AO42" s="3" t="s">
+      <c r="AQ42" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>16837700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>16993000</v>
+      </c>
+      <c r="F43" s="3">
         <v>16566900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>16555200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>16312400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>15013000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>14840000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>15987100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>15544800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>15652200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>16250700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>15561000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>16121400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>16044300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>16115200</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>5</v>
       </c>
@@ -4447,98 +4633,104 @@
       <c r="AA43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AB43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD43" s="3">
         <v>10547700</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF43" s="3">
         <v>10842600</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH43" s="3">
         <v>10658000</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ43" s="3">
         <v>10169400</v>
       </c>
-      <c r="AI43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL43" s="3">
         <v>9525100</v>
       </c>
-      <c r="AK43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN43" s="3">
         <v>9987800</v>
       </c>
-      <c r="AM43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP43" s="3">
         <v>10195700</v>
       </c>
-      <c r="AO43" s="3" t="s">
+      <c r="AQ43" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1789100</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1805600</v>
+      </c>
+      <c r="F44" s="3">
         <v>1720100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1718900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1798000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1654800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1549800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1669600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1646800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1658200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1713300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1640600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1713500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1705300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>1588100</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>5</v>
       </c>
@@ -4566,98 +4758,104 @@
       <c r="AA44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AB44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD44" s="3">
         <v>894200</v>
       </c>
-      <c r="AC44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF44" s="3">
         <v>990100</v>
       </c>
-      <c r="AE44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH44" s="3">
         <v>967600</v>
       </c>
-      <c r="AG44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ44" s="3">
         <v>834000</v>
       </c>
-      <c r="AI44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL44" s="3">
         <v>809600</v>
       </c>
-      <c r="AK44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN44" s="3">
         <v>771300</v>
       </c>
-      <c r="AM44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP44" s="3">
         <v>844700</v>
       </c>
-      <c r="AO44" s="3" t="s">
+      <c r="AQ44" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>237600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>239800</v>
+      </c>
+      <c r="F45" s="3">
         <v>169100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>169000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>312400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>287500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>172900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>186300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1536500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1547100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>949500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>909200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>340300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>338700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1373300</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>5</v>
       </c>
@@ -4685,98 +4883,104 @@
       <c r="AA45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AB45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD45" s="3">
         <v>140900</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF45" s="3">
         <v>1057600</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH45" s="3">
         <v>486200</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>839600</v>
       </c>
-      <c r="AI45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL45" s="3">
         <v>625200</v>
       </c>
-      <c r="AK45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN45" s="3">
         <v>286600</v>
       </c>
-      <c r="AM45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP45" s="3">
         <v>155200</v>
       </c>
-      <c r="AO45" s="3" t="s">
+      <c r="AQ45" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>29728100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>30002300</v>
+      </c>
+      <c r="F46" s="3">
         <v>30367500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>30346100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>29533800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>27181200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>28790800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>31016100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>29076400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>29277200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>30835600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>29526900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>29202800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>29063200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>30687200</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>5</v>
       </c>
@@ -4804,98 +5008,104 @@
       <c r="AA46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AB46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD46" s="3">
         <v>19111500</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF46" s="3">
         <v>18394100</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH46" s="3">
         <v>18130400</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ46" s="3">
         <v>15891300</v>
       </c>
-      <c r="AI46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL46" s="3">
         <v>18663300</v>
       </c>
-      <c r="AK46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN46" s="3">
         <v>17251600</v>
       </c>
-      <c r="AM46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP46" s="3">
         <v>18177000</v>
       </c>
-      <c r="AO46" s="3" t="s">
+      <c r="AQ46" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3452500</v>
+      </c>
+      <c r="E47" s="3">
+        <v>3484400</v>
+      </c>
+      <c r="F47" s="3">
         <v>3388500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>3386100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>3325900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>3061000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>3305700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>3561200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>3131900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>3153500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>3329300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>3188000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>3237100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>3221600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>3541700</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4923,98 +5133,104 @@
       <c r="AA47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AB47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD47" s="3">
         <v>4221000</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF47" s="3">
         <v>4293700</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH47" s="3">
         <v>4312300</v>
       </c>
-      <c r="AG47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ47" s="3">
         <v>3978200</v>
       </c>
-      <c r="AI47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL47" s="3">
         <v>4431700</v>
       </c>
-      <c r="AK47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN47" s="3">
         <v>4581000</v>
       </c>
-      <c r="AM47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP47" s="3">
         <v>5157400</v>
       </c>
-      <c r="AO47" s="3" t="s">
+      <c r="AQ47" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>24285400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>24509400</v>
+      </c>
+      <c r="F48" s="3">
         <v>23729000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>23712300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>22723400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>20913300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>20449300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>22029900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>20319300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>20459600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>20987100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>20096300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>20624600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>20526000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>19841800</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>5</v>
       </c>
@@ -5042,98 +5258,104 @@
       <c r="AA48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AB48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD48" s="3">
         <v>10550800</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF48" s="3">
         <v>10504100</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH48" s="3">
         <v>20596800</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>8036000</v>
       </c>
-      <c r="AI48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL48" s="3">
         <v>16368500</v>
       </c>
-      <c r="AK48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN48" s="3">
         <v>7829600</v>
       </c>
-      <c r="AM48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP48" s="3">
         <v>8424700</v>
       </c>
-      <c r="AO48" s="3" t="s">
+      <c r="AQ48" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>25109100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>25340700</v>
+      </c>
+      <c r="F49" s="3">
         <v>22780300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>22764300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>22513200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>20719800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>20569400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>22159300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>21217200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>21363700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>22168700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>21227800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>21995400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>21890300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>21451300</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>5</v>
       </c>
@@ -5161,50 +5383,56 @@
       <c r="AA49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AB49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD49" s="3">
         <v>11311300</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF49" s="3">
         <v>11282000</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH49" s="3">
         <v>16837300</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>10573400</v>
       </c>
-      <c r="AI49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL49" s="3">
         <v>10555800</v>
       </c>
-      <c r="AK49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN49" s="3">
         <v>10748100</v>
       </c>
-      <c r="AM49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP49" s="3">
         <v>11313800</v>
       </c>
-      <c r="AO49" s="3" t="s">
+      <c r="AQ49" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5322,8 +5550,14 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5441,56 +5675,62 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>123400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>124500</v>
+      </c>
+      <c r="F52" s="3">
         <v>52800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>52800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>85700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>78900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>69400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>74700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>78200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>78800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>55300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>52900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>95900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>95400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>134700</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>5</v>
       </c>
@@ -5518,50 +5758,56 @@
       <c r="AA52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AB52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD52" s="3">
         <v>1120000</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF52" s="3">
         <v>1321700</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH52" s="3">
         <v>1271700</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>1164600</v>
       </c>
-      <c r="AI52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL52" s="3">
         <v>1113200</v>
       </c>
-      <c r="AK52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN52" s="3">
         <v>1394000</v>
       </c>
-      <c r="AM52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP52" s="3">
         <v>1472300</v>
       </c>
-      <c r="AO52" s="3" t="s">
+      <c r="AQ52" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5679,56 +5925,62 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>85275900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>86062500</v>
+      </c>
+      <c r="F54" s="3">
         <v>82976400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>82918000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>80997100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>74545000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>75534700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>81373000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>76553100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>77081700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>80210000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>76805700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>77895000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>77522600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>78341300</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>5</v>
       </c>
@@ -5756,50 +6008,56 @@
       <c r="AA54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AB54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD54" s="3">
         <v>46314600</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF54" s="3">
         <v>45795600</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH54" s="3">
         <v>46481100</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ54" s="3">
         <v>39643400</v>
       </c>
-      <c r="AI54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL54" s="3">
         <v>42948300</v>
       </c>
-      <c r="AK54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN54" s="3">
         <v>41804200</v>
       </c>
-      <c r="AM54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP54" s="3">
         <v>44545200</v>
       </c>
-      <c r="AO54" s="3" t="s">
+      <c r="AQ54" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5841,8 +6099,10 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5884,56 +6144,58 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F57" s="3">
         <v>9031300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>9025000</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J57" s="3">
         <v>7944900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>8559000</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N57" s="3">
         <v>8798500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>8425100</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P57" s="3">
+      <c r="P57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R57" s="3">
         <v>8636300</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>5</v>
       </c>
@@ -5961,98 +6223,104 @@
       <c r="AA57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AB57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD57" s="3">
         <v>13271000</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF57" s="3">
         <v>11976600</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH57" s="3">
         <v>13011200</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>11186000</v>
       </c>
-      <c r="AI57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL57" s="3">
         <v>11352300</v>
       </c>
-      <c r="AK57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN57" s="3">
         <v>10772200</v>
       </c>
-      <c r="AM57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP57" s="3">
         <v>11972700</v>
       </c>
-      <c r="AO57" s="3" t="s">
+      <c r="AQ57" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12993300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>13113100</v>
+      </c>
+      <c r="F58" s="3">
         <v>10596500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>10589000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>10890200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>10022700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>9812600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>10571000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>10614000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>10687200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>8888000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>8510800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>8751300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>8709500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>7729000</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>5</v>
       </c>
@@ -6080,98 +6348,104 @@
       <c r="AA58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AB58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD58" s="3">
         <v>7013500</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF58" s="3">
         <v>5985500</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH58" s="3">
         <v>6191900</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>5417800</v>
       </c>
-      <c r="AI58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL58" s="3">
         <v>5403400</v>
       </c>
-      <c r="AK58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN58" s="3">
         <v>5262100</v>
       </c>
-      <c r="AM58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP58" s="3">
         <v>5876700</v>
       </c>
-      <c r="AO58" s="3" t="s">
+      <c r="AQ58" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>23338300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>23553600</v>
+      </c>
+      <c r="F59" s="3">
         <v>15641700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>15630600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>22595400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>20795500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>13995200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>15077000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>21979000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>22130800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>15489100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>14831700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>22404800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>22297700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>14845600</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>5</v>
       </c>
@@ -6199,98 +6473,104 @@
       <c r="AA59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AB59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD59" s="3">
         <v>997600</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF59" s="3">
         <v>1175200</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH59" s="3">
         <v>868100</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>991500</v>
       </c>
-      <c r="AI59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL59" s="3">
         <v>1068400</v>
       </c>
-      <c r="AK59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN59" s="3">
         <v>875500</v>
       </c>
-      <c r="AM59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP59" s="3">
         <v>935800</v>
       </c>
-      <c r="AO59" s="3" t="s">
+      <c r="AQ59" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>36331500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>36666700</v>
+      </c>
+      <c r="F60" s="3">
         <v>35269500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>35244600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>33485600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>30818200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>31752800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>34207000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>32592900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>32818000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>33175600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>31767600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>31156100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>31007200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>31210900</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>5</v>
       </c>
@@ -6318,98 +6598,104 @@
       <c r="AA60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AB60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD60" s="3">
         <v>21282100</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF60" s="3">
         <v>19137300</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH60" s="3">
         <v>20071300</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ60" s="3">
         <v>17595300</v>
       </c>
-      <c r="AI60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL60" s="3">
         <v>17824000</v>
       </c>
-      <c r="AK60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN60" s="3">
         <v>16909800</v>
       </c>
-      <c r="AM60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP60" s="3">
         <v>18785200</v>
       </c>
-      <c r="AO60" s="3" t="s">
+      <c r="AQ60" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>25599200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>25835400</v>
+      </c>
+      <c r="F61" s="3">
         <v>24060100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>24043200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>24439200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>22492400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>20503200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>22087900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>20664300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>20807000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>22449400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>21496600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>22713500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>22605000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>22815000</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -6438,97 +6724,103 @@
         <v>0</v>
       </c>
       <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>12177000</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
         <v>13789800</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
         <v>13099000</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="3">
         <v>9974300</v>
       </c>
-      <c r="AI61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL61" s="3">
         <v>10611100</v>
       </c>
-      <c r="AK61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN61" s="3">
         <v>10132200</v>
       </c>
-      <c r="AM61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP61" s="3">
         <v>9794300</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AQ61" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5010900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>5057100</v>
+      </c>
+      <c r="F62" s="3">
         <v>5071000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>5067500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>5174400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>4762200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>4734400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>5100400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>5161300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>5196900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>5488000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>5255100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>5667100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>5640000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>5605400</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>5</v>
       </c>
@@ -6556,50 +6848,56 @@
       <c r="AA62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AB62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD62" s="3">
         <v>4863300</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF62" s="3">
         <v>4874200</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH62" s="3">
         <v>5005400</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>4637600</v>
       </c>
-      <c r="AI62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL62" s="3">
         <v>4826000</v>
       </c>
-      <c r="AK62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN62" s="3">
         <v>5316800</v>
       </c>
-      <c r="AM62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP62" s="3">
         <v>5546400</v>
       </c>
-      <c r="AO62" s="3" t="s">
+      <c r="AQ62" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6717,8 +7015,14 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6836,8 +7140,14 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6955,56 +7265,62 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>69854900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>70499300</v>
+      </c>
+      <c r="F66" s="3">
         <v>67402800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>67355400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>66058700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>60796600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>59688400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>64301800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>61104700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>61526600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>63959300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>61244700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>62295200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>61997400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>62452700</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>5</v>
       </c>
@@ -7032,50 +7348,56 @@
       <c r="AA66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AB66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD66" s="3">
         <v>39614800</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF66" s="3">
         <v>39180900</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH66" s="3">
         <v>39538000</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ66" s="3">
         <v>33427000</v>
       </c>
-      <c r="AI66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL66" s="3">
         <v>34555600</v>
       </c>
-      <c r="AK66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN66" s="3">
         <v>33611000</v>
       </c>
-      <c r="AM66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP66" s="3">
         <v>35449100</v>
       </c>
-      <c r="AO66" s="3" t="s">
+      <c r="AQ66" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7117,8 +7439,10 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7236,8 +7560,14 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7355,8 +7685,14 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7474,8 +7810,14 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7593,8 +7935,14 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -7670,50 +8018,56 @@
       <c r="AA72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AB72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD72" s="3">
         <v>-3961300</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF72" s="3">
         <v>-4490900</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH72" s="3">
         <v>-4199200</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ72" s="3">
         <v>-4276200</v>
       </c>
-      <c r="AI72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL72" s="3">
         <v>-3625300</v>
       </c>
-      <c r="AK72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN72" s="3">
         <v>-3922400</v>
       </c>
-      <c r="AM72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP72" s="3">
         <v>-3796800</v>
       </c>
-      <c r="AO72" s="3" t="s">
+      <c r="AQ72" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7831,8 +8185,14 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7950,8 +8310,14 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8069,56 +8435,62 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12423200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>12537800</v>
+      </c>
+      <c r="F76" s="3">
         <v>12745100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>12736100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>12314700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>11333800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>13370900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>14404400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>12889700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>12978700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>13607800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>13030300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>12665900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>12605400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>13097100</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>5</v>
       </c>
@@ -8146,50 +8518,56 @@
       <c r="AA76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AB76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD76" s="3">
         <v>6699700</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF76" s="3">
         <v>6614700</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH76" s="3">
         <v>6943100</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ76" s="3">
         <v>6216400</v>
       </c>
-      <c r="AI76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL76" s="3">
         <v>8392700</v>
       </c>
-      <c r="AK76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN76" s="3">
         <v>8193200</v>
       </c>
-      <c r="AM76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP76" s="3">
         <v>9096100</v>
       </c>
-      <c r="AO76" s="3" t="s">
+      <c r="AQ76" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8307,132 +8685,144 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8478,80 +8868,86 @@
       <c r="Q81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R81" s="3">
+      <c r="R81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T81" s="3">
         <v>256800</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V81" s="3">
         <v>112500</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X81" s="3">
         <v>317900</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z81" s="3">
         <v>231100</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB81" s="3">
         <v>-150100</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD81" s="3">
         <v>331400</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF81" s="3">
         <v>389900</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH81" s="3">
         <v>175100</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>176900</v>
       </c>
-      <c r="AI81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL81" s="3">
         <v>223400</v>
       </c>
-      <c r="AK81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN81" s="3">
         <v>146800</v>
       </c>
-      <c r="AM81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP81" s="3">
         <v>234600</v>
       </c>
-      <c r="AO81" s="3" t="s">
+      <c r="AQ81" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8593,127 +8989,135 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>839700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>772800</v>
+      </c>
+      <c r="F83" s="3">
         <v>305900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>329600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>768800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>774100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>305600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>292700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>778900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>775200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>408500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>374800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>650000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>690700</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T83" s="3">
+      <c r="T83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V83" s="3">
         <v>2295300</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X83" s="3">
+      <c r="X83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z83" s="3">
         <v>2101000</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AB83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD83" s="3">
         <v>2289900</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF83" s="3">
         <v>1109700</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH83" s="3">
         <v>1095400</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>979700</v>
       </c>
-      <c r="AI83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL83" s="3">
         <v>839800</v>
       </c>
-      <c r="AK83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN83" s="3">
         <v>861100</v>
       </c>
-      <c r="AM83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP83" s="3">
         <v>969400</v>
       </c>
-      <c r="AO83" s="3" t="s">
+      <c r="AQ83" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8831,8 +9235,14 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8950,8 +9360,14 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9069,8 +9485,14 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9188,8 +9610,14 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9307,127 +9735,139 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="D89" s="3">
+        <v>807700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>815200</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H89" s="3">
         <v>811500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>746900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>1835600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1977500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>799300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>804800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1884600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1804600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>870600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>866500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>1655200</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T89" s="3">
+      <c r="T89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V89" s="3">
         <v>3411900</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X89" s="3">
+      <c r="X89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z89" s="3">
         <v>2783500</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AB89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD89" s="3">
         <v>3486400</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF89" s="3">
         <v>629500</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH89" s="3">
         <v>2665100</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ89" s="3">
         <v>652700</v>
       </c>
-      <c r="AI89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL89" s="3">
         <v>2223600</v>
       </c>
-      <c r="AK89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN89" s="3">
         <v>526500</v>
       </c>
-      <c r="AM89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP89" s="3">
         <v>2396300</v>
       </c>
-      <c r="AO89" s="3" t="s">
+      <c r="AQ89" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9469,127 +9909,135 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F91" s="3">
+      <c r="D91" s="3">
+        <v>-712300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-718900</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H91" s="3">
         <v>-759200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-698800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-851500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-917400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-707200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-712100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-994800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-952600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-731400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-727900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-848800</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-1004500</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-604100</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X91" s="3">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-1642100</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AB91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-1892400</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-791200</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-1074000</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-637800</v>
       </c>
-      <c r="AI91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-1117500</v>
       </c>
-      <c r="AK91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN91" s="3">
         <v>-560400</v>
       </c>
-      <c r="AM91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP91" s="3">
         <v>-403100</v>
       </c>
-      <c r="AO91" s="3" t="s">
+      <c r="AQ91" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9707,8 +10155,14 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9826,127 +10280,139 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="D94" s="3">
+        <v>-2150700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-2170500</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H94" s="3">
         <v>-978900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-900900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-389800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-419900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-729700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-734700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-816800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-782200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-352600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-350900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>195400</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T94" s="3">
+      <c r="T94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V94" s="3">
         <v>-922100</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X94" s="3">
+      <c r="X94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-6267700</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AB94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-288300</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-476600</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-1111300</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-676600</v>
       </c>
-      <c r="AI94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL94" s="3">
         <v>-1137800</v>
       </c>
-      <c r="AK94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN94" s="3">
         <v>-457400</v>
       </c>
-      <c r="AM94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP94" s="3">
         <v>-957800</v>
       </c>
-      <c r="AO94" s="3" t="s">
+      <c r="AQ94" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9988,127 +10454,135 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="D96" s="3">
+        <v>677500</v>
+      </c>
+      <c r="E96" s="3">
+        <v>683700</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3">
         <v>655900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>603700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>7200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>7800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>515400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>518900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>8300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>7900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>470500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>468300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>371300</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-579200</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-282900</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-746300</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-729800</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-49100</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-610200</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-60600</v>
       </c>
-      <c r="AK96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-590700</v>
       </c>
-      <c r="AM96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-24200</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AQ96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10226,8 +10700,14 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10345,8 +10825,14 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10464,361 +10950,385 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="D100" s="3">
+        <v>969400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>978300</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H100" s="3">
         <v>-1083400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-997100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-336500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-362500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-646600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-651100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-561000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-537200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-1159400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-1153800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-981000</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T100" s="3">
+      <c r="T100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V100" s="3">
         <v>2487600</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X100" s="3">
+      <c r="X100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z100" s="3">
         <v>3593400</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AB100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-1838500</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-1146300</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH100" s="3">
         <v>717700</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>-3455700</v>
       </c>
-      <c r="AI100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL100" s="3">
         <v>671000</v>
       </c>
-      <c r="AK100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN100" s="3">
         <v>-921700</v>
       </c>
-      <c r="AM100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP100" s="3">
         <v>827700</v>
       </c>
-      <c r="AO100" s="3" t="s">
+      <c r="AQ100" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-58100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-53500</v>
+      </c>
+      <c r="F101" s="3">
         <v>9300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>10000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>1100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>1100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-100000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-95800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-25700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-25500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>239300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>219600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-210000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-223200</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T101" s="3">
+      <c r="T101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V101" s="3">
         <v>68500</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X101" s="3">
+      <c r="X101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-26200</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AB101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-4400</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF101" s="3">
         <v>6900</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-6500</v>
       </c>
-      <c r="AG101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>-11300</v>
       </c>
-      <c r="AI101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL101" s="3">
         <v>3900</v>
       </c>
-      <c r="AK101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN101" s="3">
         <v>-32100</v>
       </c>
-      <c r="AM101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP101" s="3">
         <v>17400</v>
       </c>
-      <c r="AO101" s="3" t="s">
+      <c r="AQ101" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-347300</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>-350500</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-1308900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1204600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>1118600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>1205100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-575900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-579900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>406800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>389500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-667000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-663800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>1108900</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T102" s="3">
+      <c r="T102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V102" s="3">
         <v>5045800</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X102" s="3">
+      <c r="X102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z102" s="3">
         <v>83000</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AB102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD102" s="3">
         <v>1355300</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-986400</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH102" s="3">
         <v>1978800</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>-3751400</v>
       </c>
-      <c r="AI102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL102" s="3">
         <v>1762000</v>
       </c>
-      <c r="AK102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN102" s="3">
         <v>-886000</v>
       </c>
-      <c r="AM102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP102" s="3">
         <v>2335900</v>
       </c>
-      <c r="AO102" s="3" t="s">
+      <c r="AQ102" s="3" t="s">
         <v>5</v>
       </c>
     </row>
